--- a/Config/Datas/town_walker_population.xlsx
+++ b/Config/Datas/town_walker_population.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="town_walker_population" sheetId="1" r:id="R5030b91c014840f4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="town_walker_population" sheetId="1" r:id="Rbf9dfcac677b4ba7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -261,6 +261,9 @@
     <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="22" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="24" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="22" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -291,6 +294,15 @@
       <x:c r="I1" s="2" t="str">
         <x:v>walker_elite_weight</x:v>
       </x:c>
+      <x:c r="J1" t="str">
+        <x:v>resident_idle_limit</x:v>
+      </x:c>
+      <x:c r="K1" t="str">
+        <x:v>resident_idle_spawn_interval</x:v>
+      </x:c>
+      <x:c r="L1" t="str">
+        <x:v>resident_idle_cfg_id</x:v>
+      </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="2" t="str">
@@ -320,6 +332,15 @@
       <x:c r="I2" s="2" t="str">
         <x:v>int</x:v>
       </x:c>
+      <x:c r="J2" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="K2" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="L2" t="str">
+        <x:v>string</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="2" t="str">
@@ -349,6 +370,15 @@
       <x:c r="I3" s="2" t="str">
         <x:v>c,s</x:v>
       </x:c>
+      <x:c r="J3" t="str">
+        <x:v>c,s</x:v>
+      </x:c>
+      <x:c r="K3" t="str">
+        <x:v>c,s</x:v>
+      </x:c>
+      <x:c r="L3" t="str">
+        <x:v>c,s</x:v>
+      </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="2" t="str">
@@ -377,6 +407,15 @@
       </x:c>
       <x:c r="I4" s="2" t="str">
         <x:v>精英权重</x:v>
+      </x:c>
+      <x:c r="J4" t="str">
+        <x:v>固定村民数量上限</x:v>
+      </x:c>
+      <x:c r="K4" t="str">
+        <x:v>固定村民刷新间隔</x:v>
+      </x:c>
+      <x:c r="L4" t="str">
+        <x:v>固定村民单位配置</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -405,6 +444,15 @@
       <x:c r="I5" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="J5" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K5" t="n">
+        <x:v>2.5</x:v>
+      </x:c>
+      <x:c r="L5" t="str">
+        <x:v>civil_woman</x:v>
+      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6"/>
@@ -432,6 +480,15 @@
       <x:c r="I6" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="J6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K6" t="n">
+        <x:v>2.5</x:v>
+      </x:c>
+      <x:c r="L6" t="str">
+        <x:v>civil_woman</x:v>
+      </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7"/>
@@ -459,6 +516,15 @@
       <x:c r="I7" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="J7" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K7" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L7" t="str">
+        <x:v>civil_woman</x:v>
+      </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8"/>
@@ -486,6 +552,15 @@
       <x:c r="I8" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="J8" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K8" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="L8" t="str">
+        <x:v>civil_woman</x:v>
+      </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9"/>
@@ -513,6 +588,15 @@
       <x:c r="I9" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="J9" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K9" t="n">
+        <x:v>1.2</x:v>
+      </x:c>
+      <x:c r="L9" t="str">
+        <x:v>civil_woman</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
